--- a/Team-Data/2013-14/2-25-2013-14.xlsx
+++ b/Team-Data/2013-14/2-25-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,19 +728,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
         <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.464</v>
+        <v>0.473</v>
       </c>
       <c r="H2" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I2" t="n">
         <v>37.7</v>
@@ -685,67 +752,67 @@
         <v>0.459</v>
       </c>
       <c r="L2" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M2" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="O2" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P2" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R2" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S2" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T2" t="n">
         <v>40.7</v>
       </c>
       <c r="U2" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="V2" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W2" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB2" t="n">
         <v>101.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>17</v>
       </c>
       <c r="AF2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
         <v>18</v>
@@ -772,7 +839,7 @@
         <v>6</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP2" t="n">
         <v>22</v>
@@ -781,19 +848,19 @@
         <v>6</v>
       </c>
       <c r="AR2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS2" t="n">
         <v>18</v>
       </c>
       <c r="AT2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
         <v>6</v>
@@ -808,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-3.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
@@ -969,16 +1036,16 @@
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV3" t="n">
         <v>23</v>
       </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
         <v>13</v>
@@ -1154,7 +1221,7 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
@@ -1163,7 +1230,7 @@
         <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
@@ -1178,7 +1245,7 @@
         <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -1285,25 +1352,25 @@
         <v>-1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK5" t="n">
         <v>25</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1327,7 +1394,7 @@
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS5" t="n">
         <v>7</v>
@@ -1348,7 +1415,7 @@
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
         <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>0.536</v>
+        <v>0.527</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
@@ -1407,7 +1474,7 @@
         <v>34.4</v>
       </c>
       <c r="J6" t="n">
-        <v>80.7</v>
+        <v>80.5</v>
       </c>
       <c r="K6" t="n">
         <v>0.427</v>
@@ -1416,22 +1483,22 @@
         <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N6" t="n">
         <v>0.341</v>
       </c>
       <c r="O6" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P6" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="R6" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
         <v>32.9</v>
@@ -1443,10 +1510,10 @@
         <v>22.3</v>
       </c>
       <c r="V6" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W6" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
         <v>5.3</v>
@@ -1455,19 +1522,19 @@
         <v>6.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.8</v>
+        <v>92.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1503,7 +1570,7 @@
         <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>10</v>
@@ -1512,7 +1579,7 @@
         <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -1521,13 +1588,13 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" t="n">
         <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>0.379</v>
+        <v>0.386</v>
       </c>
       <c r="H7" t="n">
         <v>48.8</v>
@@ -1592,16 +1659,16 @@
         <v>85.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.423</v>
+        <v>0.424</v>
       </c>
       <c r="L7" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O7" t="n">
         <v>17.4</v>
@@ -1610,22 +1677,22 @@
         <v>23.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R7" t="n">
         <v>12.8</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U7" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V7" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W7" t="n">
         <v>7.2</v>
@@ -1637,7 +1704,7 @@
         <v>5.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA7" t="n">
         <v>20.1</v>
@@ -1649,7 +1716,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
@@ -1676,13 +1743,13 @@
         <v>20</v>
       </c>
       <c r="AM7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN7" t="n">
         <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP7" t="n">
         <v>15</v>
@@ -1691,7 +1758,7 @@
         <v>22</v>
       </c>
       <c r="AR7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS7" t="n">
         <v>16</v>
@@ -1700,19 +1767,19 @@
         <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
       </c>
       <c r="AY7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ7" t="n">
         <v>14</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -1831,13 +1898,13 @@
         <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
         <v>9</v>
@@ -1867,7 +1934,7 @@
         <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1897,7 +1964,7 @@
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
         <v>22</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>0.446</v>
+        <v>0.455</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1953,19 +2020,19 @@
         <v>37.8</v>
       </c>
       <c r="J9" t="n">
-        <v>85.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M9" t="n">
         <v>23.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="O9" t="n">
         <v>18.6</v>
@@ -1974,16 +2041,16 @@
         <v>25.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="R9" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="S9" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="T9" t="n">
-        <v>45.6</v>
+        <v>45.2</v>
       </c>
       <c r="U9" t="n">
         <v>21.8</v>
@@ -1998,7 +2065,7 @@
         <v>5.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z9" t="n">
         <v>22.8</v>
@@ -2007,19 +2074,19 @@
         <v>21.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.5</v>
+        <v>102.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
         <v>19</v>
@@ -2031,10 +2098,10 @@
         <v>14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL9" t="n">
         <v>9</v>
@@ -2058,10 +2125,10 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
         <v>13</v>
@@ -2070,13 +2137,13 @@
         <v>24</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ9" t="n">
         <v>29</v>
@@ -2088,7 +2155,7 @@
         <v>11</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2222,7 +2289,7 @@
         <v>28</v>
       </c>
       <c r="AM10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN10" t="n">
         <v>29</v>
@@ -2246,7 +2313,7 @@
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV10" t="n">
         <v>17</v>
@@ -2261,10 +2328,10 @@
         <v>16</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,13 +2456,13 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK11" t="n">
         <v>9</v>
@@ -2431,7 +2498,7 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -2481,52 +2548,52 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12" t="n">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J12" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.475</v>
+        <v>0.473</v>
       </c>
       <c r="L12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M12" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="O12" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="P12" t="n">
-        <v>31.3</v>
+        <v>31.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.697</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="T12" t="n">
         <v>45.3</v>
@@ -2535,10 +2602,10 @@
         <v>20.7</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W12" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X12" t="n">
         <v>5.8</v>
@@ -2547,22 +2614,22 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA12" t="n">
         <v>24.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.5</v>
+        <v>106.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE12" t="n">
         <v>6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
@@ -2571,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="n">
         <v>15</v>
@@ -2580,16 +2647,16 @@
         <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2604,13 +2671,13 @@
         <v>16</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,13 +2686,13 @@
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -2663,25 +2730,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.768</v>
+        <v>0.764</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="J13" t="n">
-        <v>81.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>0.453</v>
@@ -2690,7 +2757,7 @@
         <v>6.9</v>
       </c>
       <c r="M13" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N13" t="n">
         <v>0.352</v>
@@ -2702,31 +2769,31 @@
         <v>23.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R13" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="S13" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="T13" t="n">
-        <v>45.7</v>
+        <v>45.4</v>
       </c>
       <c r="U13" t="n">
         <v>20.5</v>
       </c>
       <c r="V13" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W13" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X13" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z13" t="n">
         <v>20.2</v>
@@ -2735,16 +2802,16 @@
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
@@ -2759,7 +2826,7 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
         <v>12</v>
@@ -2774,7 +2841,7 @@
         <v>19</v>
       </c>
       <c r="AO13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -2783,31 +2850,31 @@
         <v>4</v>
       </c>
       <c r="AR13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS13" t="n">
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV13" t="n">
         <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>12</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -2947,7 +3014,7 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
@@ -2965,7 +3032,7 @@
         <v>24</v>
       </c>
       <c r="AR14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
         <v>13</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -3027,34 +3094,34 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" t="n">
         <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0.445</v>
       </c>
       <c r="L15" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="N15" t="n">
         <v>0.373</v>
@@ -3063,10 +3130,10 @@
         <v>16.8</v>
       </c>
       <c r="P15" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R15" t="n">
         <v>9.4</v>
@@ -3087,13 +3154,13 @@
         <v>6.8</v>
       </c>
       <c r="X15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA15" t="n">
         <v>19.2</v>
@@ -3102,10 +3169,10 @@
         <v>100.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.6</v>
+        <v>-5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3126,10 +3193,10 @@
         <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
@@ -3144,10 +3211,10 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS15" t="n">
         <v>11</v>
@@ -3162,13 +3229,13 @@
         <v>22</v>
       </c>
       <c r="AW15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
         <v>10</v>
@@ -3180,7 +3247,7 @@
         <v>15</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF16" t="n">
         <v>11</v>
@@ -3326,7 +3393,7 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3335,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3347,7 +3414,7 @@
         <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>20</v>
@@ -3362,7 +3429,7 @@
         <v>28</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3566,7 @@
         <v>13</v>
       </c>
       <c r="AN17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO17" t="n">
         <v>13</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
         <v>12</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,7 +3736,7 @@
         <v>29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
         <v>29</v>
@@ -3690,7 +3757,7 @@
         <v>27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR18" t="n">
         <v>11</v>
@@ -3708,10 +3775,10 @@
         <v>25</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY18" t="n">
         <v>19</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" t="n">
         <v>29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.491</v>
+        <v>0.482</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3782,19 +3849,19 @@
         <v>7.6</v>
       </c>
       <c r="M19" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O19" t="n">
         <v>21.1</v>
       </c>
       <c r="P19" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.775</v>
+        <v>0.778</v>
       </c>
       <c r="R19" t="n">
         <v>12.8</v>
@@ -3803,16 +3870,16 @@
         <v>32.9</v>
       </c>
       <c r="T19" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
       <c r="U19" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V19" t="n">
         <v>13.8</v>
       </c>
       <c r="W19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X19" t="n">
         <v>3.6</v>
@@ -3821,19 +3888,19 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
@@ -3845,13 +3912,13 @@
         <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>10</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3872,16 +3939,16 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS19" t="n">
         <v>8</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AT19" t="n">
         <v>3</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>4</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
@@ -3890,16 +3957,16 @@
         <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
       </c>
       <c r="AY19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4048,7 +4115,7 @@
         <v>2</v>
       </c>
       <c r="AO20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
         <v>18</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>-1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
         <v>23</v>
@@ -4224,7 +4291,7 @@
         <v>7</v>
       </c>
       <c r="AM21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN21" t="n">
         <v>9</v>
@@ -4245,16 +4312,16 @@
         <v>28</v>
       </c>
       <c r="AT21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV21" t="n">
         <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
         <v>19</v>
@@ -4272,7 +4339,7 @@
         <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,16 +4458,16 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
         <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL22" t="n">
         <v>17</v>
@@ -4415,7 +4482,7 @@
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4442,7 +4509,7 @@
         <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -4483,52 +4550,52 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
         <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>0.288</v>
+        <v>0.293</v>
       </c>
       <c r="H23" t="n">
         <v>48.8</v>
       </c>
       <c r="I23" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J23" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O23" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P23" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="R23" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T23" t="n">
         <v>42.1</v>
@@ -4549,19 +4616,19 @@
         <v>5.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.4</v>
+        <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4579,7 +4646,7 @@
         <v>22</v>
       </c>
       <c r="AJ23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
@@ -4588,7 +4655,7 @@
         <v>19</v>
       </c>
       <c r="AM23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN23" t="n">
         <v>20</v>
@@ -4597,13 +4664,13 @@
         <v>23</v>
       </c>
       <c r="AP23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ23" t="n">
         <v>13</v>
       </c>
       <c r="AR23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
         <v>12</v>
@@ -4612,19 +4679,19 @@
         <v>23</v>
       </c>
       <c r="AU23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AZ23" t="n">
         <v>8</v>
@@ -4636,7 +4703,7 @@
         <v>24</v>
       </c>
       <c r="BC23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -4743,13 +4810,13 @@
         <v>-10.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
       </c>
       <c r="AF24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
         <v>14</v>
@@ -4803,7 +4870,7 @@
         <v>2</v>
       </c>
       <c r="AX24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -4847,64 +4914,64 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" t="n">
         <v>33</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>0.589</v>
+        <v>0.6</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J25" t="n">
-        <v>84.5</v>
+        <v>84.3</v>
       </c>
       <c r="K25" t="n">
         <v>0.458</v>
       </c>
       <c r="L25" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="M25" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="O25" t="n">
         <v>18.4</v>
       </c>
       <c r="P25" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="Q25" t="n">
         <v>0.76</v>
       </c>
       <c r="R25" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S25" t="n">
         <v>31.9</v>
       </c>
       <c r="T25" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U25" t="n">
         <v>19.1</v>
       </c>
       <c r="V25" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W25" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X25" t="n">
         <v>4.9</v>
@@ -4913,25 +4980,25 @@
         <v>4.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA25" t="n">
         <v>21.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>105</v>
+        <v>105.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
       </c>
       <c r="AF25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG25" t="n">
         <v>10</v>
@@ -4943,25 +5010,25 @@
         <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="n">
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
         <v>15</v>
@@ -4985,7 +5052,7 @@
         <v>8</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
@@ -5000,7 +5067,7 @@
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -5029,70 +5096,70 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F26" t="n">
         <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39.5</v>
+        <v>39.8</v>
       </c>
       <c r="J26" t="n">
-        <v>87.8</v>
+        <v>88</v>
       </c>
       <c r="K26" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L26" t="n">
         <v>9.4</v>
       </c>
       <c r="M26" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="N26" t="n">
         <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="P26" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="Q26" t="n">
         <v>0.822</v>
       </c>
       <c r="R26" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S26" t="n">
         <v>33.4</v>
       </c>
       <c r="T26" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U26" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V26" t="n">
         <v>13.7</v>
       </c>
       <c r="W26" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="X26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
         <v>19.3</v>
@@ -5101,16 +5168,16 @@
         <v>20.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>107.7</v>
+        <v>107.8</v>
       </c>
       <c r="AC26" t="n">
         <v>4.2</v>
       </c>
       <c r="AD26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE26" t="n">
         <v>6</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>5</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
@@ -5119,31 +5186,31 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
       </c>
       <c r="AJ26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL26" t="n">
         <v>3</v>
       </c>
-      <c r="AK26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2</v>
-      </c>
       <c r="AM26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO26" t="n">
         <v>6</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5167,16 +5234,16 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E27" t="n">
         <v>20</v>
       </c>
       <c r="F27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G27" t="n">
-        <v>0.351</v>
+        <v>0.357</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,10 +5296,10 @@
         <v>37.1</v>
       </c>
       <c r="J27" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L27" t="n">
         <v>6.6</v>
@@ -5241,37 +5308,37 @@
         <v>19.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O27" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="P27" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R27" t="n">
         <v>11.9</v>
       </c>
       <c r="S27" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T27" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U27" t="n">
         <v>19.3</v>
       </c>
       <c r="V27" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W27" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y27" t="n">
         <v>5.6</v>
@@ -5286,19 +5353,19 @@
         <v>101.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.4</v>
+        <v>-1.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
         <v>11</v>
@@ -5313,7 +5380,7 @@
         <v>17</v>
       </c>
       <c r="AL27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM27" t="n">
         <v>24</v>
@@ -5328,7 +5395,7 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AR27" t="n">
         <v>9</v>
@@ -5346,13 +5413,13 @@
         <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX27" t="n">
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ27" t="n">
         <v>30</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>5.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5483,7 +5550,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5498,7 +5565,7 @@
         <v>14</v>
       </c>
       <c r="AM28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
@@ -5510,7 +5577,7 @@
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5528,16 +5595,16 @@
         <v>15</v>
       </c>
       <c r="AW28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY28" t="n">
         <v>18</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA28" t="n">
         <v>24</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F29" t="n">
         <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5602,10 +5669,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O29" t="n">
         <v>18.9</v>
@@ -5617,16 +5684,16 @@
         <v>0.775</v>
       </c>
       <c r="R29" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S29" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T29" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U29" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V29" t="n">
         <v>14.1</v>
@@ -5638,7 +5705,7 @@
         <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z29" t="n">
         <v>22.7</v>
@@ -5650,10 +5717,10 @@
         <v>99.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5671,13 +5738,13 @@
         <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="n">
         <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
@@ -5686,7 +5753,7 @@
         <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP29" t="n">
         <v>9</v>
@@ -5701,7 +5768,7 @@
         <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU29" t="n">
         <v>18</v>
@@ -5710,13 +5777,13 @@
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
         <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>28</v>
@@ -5728,7 +5795,7 @@
         <v>17</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5902,13 @@
         <v>-5.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
       </c>
       <c r="AF30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG30" t="n">
         <v>24</v>
@@ -5853,7 +5920,7 @@
         <v>26</v>
       </c>
       <c r="AJ30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
         <v>22</v>
@@ -5874,7 +5941,7 @@
         <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
         <v>18</v>
@@ -5892,7 +5959,7 @@
         <v>13</v>
       </c>
       <c r="AW30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX30" t="n">
         <v>17</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
@@ -5939,85 +6006,85 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.509</v>
+        <v>0.5</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
       </c>
       <c r="I31" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J31" t="n">
         <v>84.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L31" t="n">
         <v>7.8</v>
       </c>
       <c r="M31" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.383</v>
+        <v>0.38</v>
       </c>
       <c r="O31" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P31" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.728</v>
+        <v>0.727</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S31" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T31" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U31" t="n">
         <v>23.2</v>
       </c>
       <c r="V31" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W31" t="n">
         <v>8.6</v>
       </c>
       <c r="X31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y31" t="n">
         <v>3.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6035,19 +6102,19 @@
         <v>12</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
       </c>
       <c r="AM31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO31" t="n">
         <v>28</v>
@@ -6065,7 +6132,7 @@
         <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU31" t="n">
         <v>8</v>
@@ -6077,22 +6144,22 @@
         <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-25-2013-14</t>
+          <t>2014-02-25</t>
         </is>
       </c>
     </row>
